--- a/artfynd/A 45797-2021 artfynd.xlsx
+++ b/artfynd/A 45797-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -894,6 +894,372 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133886310</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91885</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Matterabäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>489152</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6660470</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133886157</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58444</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Matterabäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>489146</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6660489</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133886202</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Matterabäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>489146</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6660489</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>

--- a/artfynd/A 45797-2021 artfynd.xlsx
+++ b/artfynd/A 45797-2021 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>133886310</v>
       </c>
       <c r="B4" t="n">
-        <v>91885</v>
+        <v>91889</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45797-2021 artfynd.xlsx
+++ b/artfynd/A 45797-2021 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>133886310</v>
       </c>
       <c r="B4" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45797-2021 artfynd.xlsx
+++ b/artfynd/A 45797-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133395978</v>
       </c>
       <c r="B2" t="n">
-        <v>58332</v>
+        <v>58339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>133395960</v>
       </c>
       <c r="B3" t="n">
-        <v>58119</v>
+        <v>58126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>133886310</v>
       </c>
       <c r="B4" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>133886157</v>
       </c>
       <c r="B5" t="n">
-        <v>58444</v>
+        <v>58451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>133886202</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45797-2021 artfynd.xlsx
+++ b/artfynd/A 45797-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133395978</v>
       </c>
       <c r="B2" t="n">
-        <v>58339</v>
+        <v>58349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>133395960</v>
       </c>
       <c r="B3" t="n">
-        <v>58126</v>
+        <v>58136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>133886310</v>
       </c>
       <c r="B4" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>133886157</v>
       </c>
       <c r="B5" t="n">
-        <v>58451</v>
+        <v>58461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>133886202</v>
       </c>
       <c r="B6" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45797-2021 artfynd.xlsx
+++ b/artfynd/A 45797-2021 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>133886310</v>
       </c>
       <c r="B4" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45797-2021 artfynd.xlsx
+++ b/artfynd/A 45797-2021 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>133886310</v>
       </c>
       <c r="B4" t="n">
-        <v>91923</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45797-2021 artfynd.xlsx
+++ b/artfynd/A 45797-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133395978</v>
+        <v>133886310</v>
       </c>
       <c r="B2" t="n">
-        <v>58349</v>
+        <v>91937</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,35 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488990</v>
+        <v>489152</v>
       </c>
       <c r="R2" t="n">
-        <v>6660569</v>
+        <v>6660470</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,12 +743,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,8 +767,14 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -788,46 +795,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133395960</v>
+        <v>133395942</v>
       </c>
       <c r="B3" t="n">
-        <v>58136</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489155</v>
+        <v>489178</v>
       </c>
       <c r="R3" t="n">
-        <v>6660477</v>
+        <v>6660422</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,8 +877,14 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -901,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133886310</v>
+        <v>133886202</v>
       </c>
       <c r="B4" t="n">
-        <v>91930</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,26 +916,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489152</v>
+        <v>489146</v>
       </c>
       <c r="R4" t="n">
-        <v>6660470</v>
+        <v>6660489</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,14 +1006,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1021,32 +1028,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133886157</v>
+        <v>133395978</v>
       </c>
       <c r="B5" t="n">
-        <v>58461</v>
+        <v>58349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1068,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489146</v>
+        <v>488990</v>
       </c>
       <c r="R5" t="n">
-        <v>6660489</v>
+        <v>6660569</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1098,22 +1105,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>02:30</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,32 +1141,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133886202</v>
+        <v>133886157</v>
       </c>
       <c r="B6" t="n">
-        <v>57972</v>
+        <v>58461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1181,7 +1178,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1260,6 +1257,355 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133395960</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Matterabäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>489155</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6660477</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133395988</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Matterabäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>488990</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6660569</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133886217</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Matterabäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>489146</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6660489</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>

--- a/artfynd/A 45797-2021 artfynd.xlsx
+++ b/artfynd/A 45797-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -792,6 +797,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133886310</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133395942</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133886202</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133395978</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,6 +1286,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133886157</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1374,6 +1404,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133395960</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1487,6 +1522,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133395988</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1610,8 +1650,23 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133886217</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>